--- a/R4.5/Peso_Estructura_NOSE_DOCK_H5_H6_R4.5.xlsx
+++ b/R4.5/Peso_Estructura_NOSE_DOCK_H5_H6_R4.5.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Modos utilizados</t>
+          <t>Modos utilizados (el .STD ya pide 100)</t>
         </is>
       </c>
       <c r="E6" s="17" t="n">
@@ -745,11 +745,11 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Participación modal X (%) — R4.4, pendiente R4.5</t>
+          <t>Participación modal X (%) — R4.5, 50 modos</t>
         </is>
       </c>
       <c r="E7" s="17" t="n">
-        <v>92.07899999999999</v>
+        <v>91.253</v>
       </c>
     </row>
     <row r="8">
@@ -763,11 +763,11 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Participación modal Z (%) — R4.4, pendiente R4.5</t>
+          <t>Participación modal Z (%) — R4.5, 50 modos</t>
         </is>
       </c>
       <c r="E8" s="17" t="n">
-        <v>92.22499999999999</v>
+        <v>89.745</v>
       </c>
     </row>
     <row r="9">
@@ -823,21 +823,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Factor espectro X (R4.4, recalibrar con .ANL R4.5)</t>
+          <t>Factor espectro X (.ANL R4.5)</t>
         </is>
       </c>
       <c r="B14" s="70" t="n">
-        <v>1.5377</v>
+        <v>1.1599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Factor espectro Z (R4.4, recalibrar con .ANL R4.5)</t>
+          <t>Factor espectro Z (.ANL R4.5)</t>
         </is>
       </c>
       <c r="B15" s="70" t="n">
-        <v>2.7081</v>
+        <v>2.0938</v>
       </c>
     </row>
     <row r="16">
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" style="66" min="1" max="1"/>
@@ -1450,12 +1450,6 @@
       </c>
       <c r="H19" s="55" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H2"/>
@@ -1470,7 +1464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="66" min="1" max="1"/>
@@ -2147,13 +2141,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H2"/>
